--- a/baristaboard_input_20260515.xlsx
+++ b/baristaboard_input_20260515.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24y1034\Desktop\BaristaBoard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB60BE2-89F4-4FE0-8EA2-8E285739EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1259F66-009A-455E-B383-21CD62AEE948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7460" yWindow="1810" windowWidth="11520" windowHeight="8260" xr2:uid="{C0CE2323-85E5-45FF-858F-E7BD9299A26A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C0CE2323-85E5-45FF-858F-E7BD9299A26A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -509,10 +509,10 @@
         <v>46143</v>
       </c>
       <c r="C2" s="2">
-        <v>0.27083333333333331</v>
+        <v>0.3125</v>
       </c>
       <c r="D2" s="2">
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -523,10 +523,10 @@
         <v>46143</v>
       </c>
       <c r="C3" s="2">
-        <v>0.27083333333333331</v>
+        <v>0.3125</v>
       </c>
       <c r="D3" s="2">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -540,7 +540,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2">
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -551,10 +551,10 @@
         <v>46143</v>
       </c>
       <c r="C5" s="2">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="2">
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -565,10 +565,10 @@
         <v>46143</v>
       </c>
       <c r="C6" s="2">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D6" s="2">
-        <v>0.90625</v>
+        <v>0.86458333333333337</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -582,7 +582,7 @@
         <v>0.625</v>
       </c>
       <c r="D7" s="2">
-        <v>0.90625</v>
+        <v>0.86458333333333337</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -593,10 +593,10 @@
         <v>46143</v>
       </c>
       <c r="C8" s="2">
-        <v>0.70833333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D8" s="2">
-        <v>0.90625</v>
+        <v>0.79166666666666663</v>
       </c>
     </row>
   </sheetData>
